--- a/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91871ACD-B02E-4254-8B23-EE8C8784B4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C6EBA0-3899-4AA8-B7EF-AD52223FC2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7005,7 +7005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9EA3A66-5984-46D1-8DAB-652BFC8B4949}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330D8075-75AB-4870-89DE-C8A574E97B1F}">
   <dimension ref="B2:AF1166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32556,7 +32556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E81D108-2B59-4C78-A78F-07A86139033C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79142A11-CDBA-44D3-A90D-92602A673F10}">
   <dimension ref="B9:L100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C6EBA0-3899-4AA8-B7EF-AD52223FC2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FC48187-63EF-4532-AFE3-A220B653412F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7005,7 +7005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330D8075-75AB-4870-89DE-C8A574E97B1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F80BE7C5-6A53-4ABD-812B-2A4B454A10AA}">
   <dimension ref="B2:AF1166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32556,7 +32556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79142A11-CDBA-44D3-A90D-92602A673F10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E97830-A8B3-4FE5-97CC-008EC2811526}">
   <dimension ref="B9:L100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FC48187-63EF-4532-AFE3-A220B653412F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{450156D7-AB65-45E0-AD15-3F685BDC41C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8051" uniqueCount="2130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8061" uniqueCount="2133">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -6516,6 +6516,15 @@
   </si>
   <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>Trd_electricity import</t>
+  </si>
+  <si>
+    <t>e_CA164-315,e_CA184-500,e_CA185-500,e_CA191-500,e_CA216-315,e_CA218-315,e_CA219-315,e_CA229-345,e_CA239-315,e_CA246-315,e_CA248-315,e_CA250-315,e_CA256-315,e_CA257-315,e_CA261-315,e_CA265-315,e_CA28-287,e_CA29-287,e_CA293-315,e_CA298-315,e_CA30-287,e_CA302-315,e_CA303-315,e_CA305-315,e_CA307-315,e_CA310-315,e_CA317-315,e_CA323-315,e_CA337-345,e_CA343-765,e_CA364-500,e_CA369-500,e_CA370-500,e_CA374-500,e_CA387-500,e_CA390-500,e_CA444-345,e_r10383760-500,e_r11990161-735,e_w101946689-315,e_w104084354-315,e_w104087942-315,e_w1042251776-315,e_w1066689518-315,e_w110303217-315,e_w110303217-735,e_w1116379982-345,e_w1132335692-315,e_w113855788-500,e_w117228972-345,e_w117955755-345,e_w124919871-315,e_w129284212-315,e_w129284212-735,e_w129284212-765,e_w136145755-345,e_w142578254-315,e_w156738152-500,e_w156738153-500,e_w166474302-315,e_w166475010-315,e_w166475153-315,e_w166899876-500,e_w167808338-315,e_w167860256-315,e_w168115738-315,e_w172651669-287,e_w191437318-315,e_w227671365-315,e_w232194254-315,e_w240310383-345,e_w24364552-315,e_w25495523-500,e_w25500667-500,e_w26103715-500,e_w26296871-315,e_w264390223-315,e_w272219026-345,e_w273639295-500,e_w302580598-315,e_w323564265-315,e_w32963410-500,e_w33144100-315,e_w33144100-735,e_w33728777-500,e_w34040833-315,e_w34317219-315,e_w38223686-315,e_w44138477-315,e_w44912776-315,e_w476702648-500,e_w486371739-345,e_w5065566-500,e_w511092191-315,e_w551510936-345,e_w581354518-345,e_w614612290-500,e_w637681518-735,e_w638388421-315,e_w67214412-500,e_w711797215-345,e_w72838752-315,e_w72838752-735,e_w792464552-315,e_w80575562-315,e_w805809222-315,e_w849603970-315,e_w90870078-287,e_w92544660-315,e_w94212756-315,e_w947757905-315,e_w960912589-315,e_w961152437-315,e_w961152437-735,e_w96456442-315,e_w96456442-735</t>
+  </si>
+  <si>
+    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -7005,11 +7014,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F80BE7C5-6A53-4ABD-812B-2A4B454A10AA}">
-  <dimension ref="B2:AF1166"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A73AB95-6842-4C52-80EA-7EEC10FD7F88}">
+  <dimension ref="B2:AJ1166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -7022,8 +7031,11 @@
       <c r="U2" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -7075,8 +7087,17 @@
       <c r="AA3" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>689</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>126</v>
       </c>
@@ -7143,8 +7164,17 @@
       <c r="AF4" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH4" t="s">
+        <v>2130</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>2131</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>127</v>
       </c>
@@ -7208,8 +7238,17 @@
       <c r="AF5" t="s">
         <v>2128</v>
       </c>
-    </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH5" t="s">
+        <v>2132</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>2131</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>128</v>
       </c>
@@ -7274,7 +7313,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>129</v>
       </c>
@@ -7324,7 +7363,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>130</v>
       </c>
@@ -7374,7 +7413,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>131</v>
       </c>
@@ -7424,7 +7463,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>132</v>
       </c>
@@ -7474,7 +7513,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>133</v>
       </c>
@@ -7524,7 +7563,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>134</v>
       </c>
@@ -7574,7 +7613,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>135</v>
       </c>
@@ -7624,7 +7663,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>136</v>
       </c>
@@ -7674,7 +7713,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>137</v>
       </c>
@@ -7724,7 +7763,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>138</v>
       </c>
@@ -32556,7 +32595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E97830-A8B3-4FE5-97CC-008EC2811526}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9648CD47-F919-462E-9F33-4586BAAFF10A}">
   <dimension ref="B9:L100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{450156D7-AB65-45E0-AD15-3F685BDC41C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2476AC-F15D-4EA1-8510-77B280A4826A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8061" uniqueCount="2133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8051" uniqueCount="2130">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -6516,15 +6516,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_CA164-315,e_CA184-500,e_CA185-500,e_CA191-500,e_CA216-315,e_CA218-315,e_CA219-315,e_CA229-345,e_CA239-315,e_CA246-315,e_CA248-315,e_CA250-315,e_CA256-315,e_CA257-315,e_CA261-315,e_CA265-315,e_CA28-287,e_CA29-287,e_CA293-315,e_CA298-315,e_CA30-287,e_CA302-315,e_CA303-315,e_CA305-315,e_CA307-315,e_CA310-315,e_CA317-315,e_CA323-315,e_CA337-345,e_CA343-765,e_CA364-500,e_CA369-500,e_CA370-500,e_CA374-500,e_CA387-500,e_CA390-500,e_CA444-345,e_r10383760-500,e_r11990161-735,e_w101946689-315,e_w104084354-315,e_w104087942-315,e_w1042251776-315,e_w1066689518-315,e_w110303217-315,e_w110303217-735,e_w1116379982-345,e_w1132335692-315,e_w113855788-500,e_w117228972-345,e_w117955755-345,e_w124919871-315,e_w129284212-315,e_w129284212-735,e_w129284212-765,e_w136145755-345,e_w142578254-315,e_w156738152-500,e_w156738153-500,e_w166474302-315,e_w166475010-315,e_w166475153-315,e_w166899876-500,e_w167808338-315,e_w167860256-315,e_w168115738-315,e_w172651669-287,e_w191437318-315,e_w227671365-315,e_w232194254-315,e_w240310383-345,e_w24364552-315,e_w25495523-500,e_w25500667-500,e_w26103715-500,e_w26296871-315,e_w264390223-315,e_w272219026-345,e_w273639295-500,e_w302580598-315,e_w323564265-315,e_w32963410-500,e_w33144100-315,e_w33144100-735,e_w33728777-500,e_w34040833-315,e_w34317219-315,e_w38223686-315,e_w44138477-315,e_w44912776-315,e_w476702648-500,e_w486371739-345,e_w5065566-500,e_w511092191-315,e_w551510936-345,e_w581354518-345,e_w614612290-500,e_w637681518-735,e_w638388421-315,e_w67214412-500,e_w711797215-345,e_w72838752-315,e_w72838752-735,e_w792464552-315,e_w80575562-315,e_w805809222-315,e_w849603970-315,e_w90870078-287,e_w92544660-315,e_w94212756-315,e_w947757905-315,e_w960912589-315,e_w961152437-315,e_w961152437-735,e_w96456442-315,e_w96456442-735</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -7015,10 +7006,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A73AB95-6842-4C52-80EA-7EEC10FD7F88}">
-  <dimension ref="B2:AJ1166"/>
+  <dimension ref="B2:AF1166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -7031,11 +7022,8 @@
       <c r="U2" t="s">
         <v>794</v>
       </c>
-      <c r="AH2" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -7087,17 +7075,8 @@
       <c r="AA3" t="s">
         <v>688</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>689</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>126</v>
       </c>
@@ -7164,17 +7143,8 @@
       <c r="AF4" t="s">
         <v>2127</v>
       </c>
-      <c r="AH4" t="s">
-        <v>2130</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>2131</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>127</v>
       </c>
@@ -7238,17 +7208,8 @@
       <c r="AF5" t="s">
         <v>2128</v>
       </c>
-      <c r="AH5" t="s">
-        <v>2132</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>2131</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>128</v>
       </c>
@@ -7313,7 +7274,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>129</v>
       </c>
@@ -7363,7 +7324,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>130</v>
       </c>
@@ -7413,7 +7374,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>131</v>
       </c>
@@ -7463,7 +7424,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>132</v>
       </c>
@@ -7513,7 +7474,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>133</v>
       </c>
@@ -7563,7 +7524,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>134</v>
       </c>
@@ -7613,7 +7574,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>135</v>
       </c>
@@ -7663,7 +7624,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>136</v>
       </c>
@@ -7713,7 +7674,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>137</v>
       </c>
@@ -7763,7 +7724,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>138</v>
       </c>

--- a/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2476AC-F15D-4EA1-8510-77B280A4826A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1365E480-FFFF-4807-B8FA-953E531CD449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -6651,7 +6651,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -6668,6 +6668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -36573,12 +36574,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -36603,8 +36604,11 @@
       <c r="H19" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I19" s="14">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -36634,7 +36638,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -36664,7 +36668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -36694,7 +36698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -36713,15 +36717,16 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <f>I11</f>
+        <v>0.5</v>
+      </c>
+      <c r="G23">
         <v>1</v>
-      </c>
-      <c r="G23">
-        <f>J11</f>
-        <v>3</v>
       </c>
       <c r="H23">
         <v>4</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
